--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260806.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260806.xlsx
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>玉山金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>355,756,745</t>
+          <t>70,605,743</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>玉山金</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>70,605,743</t>
+          <t>355,756,745</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>72,300,070</t>
+          <t>26,677,384</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>26,677,384</t>
+          <t>89,237,737</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>89,237,737</t>
+          <t>72,300,070</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>26,698,825</t>
+          <t>10,798,500</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>10,798,500</t>
+          <t>26,698,825</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
